--- a/opportunities.xlsx
+++ b/opportunities.xlsx
@@ -414,7 +414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>

--- a/opportunities.xlsx
+++ b/opportunities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O160"/>
+  <dimension ref="A1:O286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12423,6 +12423,9456 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>535ef0cbe764</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=e663b8c3b6aa0853d0bff63740e87749f702b20119212bba6981aa262943cc37JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0249eaf8-bec0-60c6-2a24-fd9fbf06616a&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0wMjQ5ZWFmOGJlYzA2MGM2MmEyNGZkOWZiZjA2NjE2YQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like Drift Boss, where one wrong turn sends you off the edge, or skill …</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:49 UTC</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2e6dae2d526c</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9f46847a024e57da358e5172aa5c4102022b44f15aaa070b5503bb4b03f6f1aJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0249eaf8-bec0-60c6-2a24-fd9fbf06616a&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:49 UTC</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>6298f65b0b53</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=15f9439c8c1d45633925ae7dd4a17b060259b4258b3dd23c5e43a805da81531cJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0249eaf8-bec0-60c6-2a24-fd9fbf06616a&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. Have fun!</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:49 UTC</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>60ff478cbdce</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ab7f0fdc31f387d6bd471cfa35af9c6cdbff81a07b3bcd4b71c7e52170cfda5JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0249eaf8-bec0-60c6-2a24-fd9fbf06616a&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:49 UTC</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>368fa554a8b8</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=547983a873867955f2cd23b271f9bd160bbc78cd7c9d7621e35af586dc26c33eJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0249eaf8-bec0-60c6-2a24-fd9fbf06616a&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, Crime and Comedy. Watch now.</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:49 UTC</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>3e8cfa49015e</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=86be8db27baad767a3e484ec51b6530100d40d46735a0a899d1ab6066c511eceJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0249eaf8-bec0-60c6-2a24-fd9fbf06616a&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and promo codes to save you over 50% on purchases.</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:49 UTC</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>5093f2c4a8b3</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=22e10397ecf70e9bf28108bdfa4a5fc45e656bd848538c8ac9351587a6104b0eJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0249eaf8-bec0-60c6-2a24-fd9fbf06616a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) and Simon Kirke (drums, percussion).</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>1</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:50 UTC</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>5d1519e5938a</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=0025987226d673ed53592b838346d0dbbd3047a754864a56bb43705fb38981b4JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cde68f-1061-61dc-0b97-f1e8116160c1&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0yNGNkZTY4ZjEwNjE2MWRjMGI5N2YxZTgxMTYxNjBjMQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like Drift Boss, where one wrong turn sends you off the edge, or skill …</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:55 UTC</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>92eb17d4f7a9</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=9142a7853d0844e037c3014b5029cc3a7bdc364cb2c821acc22373c5b74af22eJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cde68f-1061-61dc-0b97-f1e8116160c1&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:55 UTC</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>0971e4bb2a2e</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=cd4f5efdcd3e9fb87173ad0ed567e443df0a5981165f82c10f6c3645824da1d7JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cde68f-1061-61dc-0b97-f1e8116160c1&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. Have fun!</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:55 UTC</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>3ade0c9083b8</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f52857ec7e20f8f266f45aeab9cc722dfdd82ac16fef28ccecfed33cd54a005JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cde68f-1061-61dc-0b97-f1e8116160c1&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:56 UTC</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>5777b811eb65</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a8ae7cac146bd9ea2848b3a7c046dbee89777007f571dec009705b1c9c9e9d3JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cde68f-1061-61dc-0b97-f1e8116160c1&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, Crime and Comedy. Watch now.</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:56 UTC</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>43dc5f4a28e3</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=03f074a7e4f1f46939b277f90dc2d96988d8d64b810c798f012be3ad665e97d4JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cde68f-1061-61dc-0b97-f1e8116160c1&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and promo codes to save you over 50% on purchases.</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:56 UTC</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>a8d01dcb91cc</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=2451746a40393d99b1ec66c2639986a1f0f6229afcf3159d2099a35886ffb491JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=24cde68f-1061-61dc-0b97-f1e8116160c1&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) and Simon Kirke (drums, percussion).</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:31:56 UTC</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>6c52d0a2949b</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ce2ba1df24c18fd6fa5adef84a0d5c5762adf054db584523c51ebb71a4056d4JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35f94dc1-af7c-6aef-1895-5aa6ae456bfd&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0zNWY5NGRjMWFmN2M2YWVmMTg5NTVhYTZhZTQ1NmJmZA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like Drift Boss, where one wrong turn sends you off the edge, or skill …</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:01 UTC</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>cd1248d453b2</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=c53afeec037f397eea997f7fe1039bba42313ac49a2353c8c61f81b4d4b76be9JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35f94dc1-af7c-6aef-1895-5aa6ae456bfd&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:01 UTC</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>c96b4f3f7b6a</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed36da28cb2f162baaad9f31501636b11148e02ca8f4b97c9c245b25e32ff387JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35f94dc1-af7c-6aef-1895-5aa6ae456bfd&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. Have fun!</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:01 UTC</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1e54447f00aa</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6828b5b234abd38736206d49e4f4a54e713e1f34e89af5a535fe8cadcc6bb52JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35f94dc1-af7c-6aef-1895-5aa6ae456bfd&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:01 UTC</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>c4cf7c4b84a2</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9d62efe606efefa8046eba0b13df1cc6c08e5a34e5e635327567c93aaee4f6eJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35f94dc1-af7c-6aef-1895-5aa6ae456bfd&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, Crime and Comedy. Watch now.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:01 UTC</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>65207fe0522a</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c80ef7ad8639ba649649b9f3513ea5efd652a86bdf402a01f49f183a5c0c7c2JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35f94dc1-af7c-6aef-1895-5aa6ae456bfd&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and promo codes to save you over 50% on purchases.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:01 UTC</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>7b24899b29b9</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=59c2e346c913dc70c52c0749f2fb2a13967ed52ea214ba083f74e5fee1ae0018JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35f94dc1-af7c-6aef-1895-5aa6ae456bfd&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) and Simon Kirke (drums, percussion).</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:01 UTC</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>428d65160b76</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6323586fed24c56c88500ab222e5fd7587307fa7cdc3e207d47230fcab999b4JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05194477-ca54-6422-3243-5310cb206520&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0wNTE5NDQ3N2NhNTQ2NDIyMzI0MzUzMTBjYjIwNjUyMA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like Drift Boss, where one wrong turn sends you off the edge, or skill …</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:06 UTC</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>041fbf4d89b9</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=e98fd2ce28283278290eba9de8010ed4fde121e8ef3c516cfaeb8ce5b1e1d4f9JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05194477-ca54-6422-3243-5310cb206520&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:06 UTC</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>d8e62828824e</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=7facda4be5b4e6251f05051076507148405c954009ea269d400b7fa780926abfJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05194477-ca54-6422-3243-5310cb206520&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. Have fun!</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:07 UTC</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>88b7ce8e2974</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ed3cb4dc06b6632d89b9b0ed01858b5295199444ef211dcba3fc6d2159c27e3JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05194477-ca54-6422-3243-5310cb206520&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:07 UTC</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>468519b32a01</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=c09bd9bd9c0b0ee7b6f449586357a9a2ca7fa8779326484e2412b460151124ffJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05194477-ca54-6422-3243-5310cb206520&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, Crime and Comedy. Watch now.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:07 UTC</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>3d302dfde3ba</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1a955d244734cfd20ca140bb39e683cf1426464d89a0fd209eeb33982264f19JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05194477-ca54-6422-3243-5310cb206520&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and promo codes to save you over 50% on purchases.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:07 UTC</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>351ee1905763</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c033f441336659ffe9bbf79c26df3f25cc3b413f38d668b76dda4be1ba8e392JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05194477-ca54-6422-3243-5310cb206520&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) and Simon Kirke (drums, percussion).</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:07 UTC</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>33600bd2da30</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Best Buy | Official Online Store | Shop Now &amp; Save</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=446c489035af8c7f83a8b7255365361d85cae3b34bcf0d41b7342d8d1fbb61b6JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0133db7a-f669-691b-260a-cc1df77f6879&amp;u=a1aHR0cHM6Ly93d3cuYmVzdGJ1eS5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Shop Best Buy for electronics, computers, appliances, cell phones, video games &amp; more new tech. Store pickup &amp; free 2-day shipping on thousands of items.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:20 UTC</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>6809743db5d7</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>BEST Definition &amp; Meaning - Merriam-Webster</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a7dcb41a7292b235971b0c48835424c4df6bbd3fbdc9943425101a3cb9e552cJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0133db7a-f669-691b-260a-cc1df77f6879&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>May 21, 2026 · Cruise ships are perhaps best known for amenities like buffets and swimming pools, but their medical facilities also have the capability to treat a wide range of illnesses and injuries, from …</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:20 UTC</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2afcc198ae7b</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Best: Definition, Meaning, and Examples - usdictionary.com</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ffdd8f6d35be7d93ec13cb451e586aed48ae7d32d04288bda3e2983dd19e842JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0133db7a-f669-691b-260a-cc1df77f6879&amp;u=a1aHR0cHM6Ly91c2RpY3Rpb25hcnkuY29tL2RlZmluaXRpb25zL2Jlc3Qv&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Oct 14, 2024 · Explore the definition of the word "best," as well as its versatile usage, synonyms, examples, etymology, and more.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:20 UTC</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>b85c65cf0570</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>BEST | English meaning - Cambridge Dictionary</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d937a177c12b158cc62aec57f00368ec08e843187515947c9032c399a0bd384JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0133db7a-f669-691b-260a-cc1df77f6879&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>BEST definition: 1. of the highest quality, or being the most suitable, pleasing, or effective type of thing or…. Learn more.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:21 UTC</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>f077068a48a4</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>best - WordReference.com Dictionary of English</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=d714ce6ac5a10eb9ee1cc670014199e7ed51aeda26ea6f551026bfb06b6a5548JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0133db7a-f669-691b-260a-cc1df77f6879&amp;u=a1aHR0cHM6Ly93d3cud29yZHJlZmVyZW5jZS5jb20vZGVmaW5pdGlvbi9iZXN0&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Affiliate</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Idioms (all) for the best, producing good as the final result: It turned out to be all for the best when I didn't get that job. Idioms as best one can, in the best way possible: As best I can tell, we're the first ones …</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:21 UTC</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>affiliate,referral</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>576cfecffe04</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>BEST Definition &amp; Meaning | Dictionary.com</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b720439fefeae113e51c5262c24c26af824ac9116d8be2c1fc73a4cda4ac3caJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0133db7a-f669-691b-260a-cc1df77f6879&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>BEST definition: of the highest quality, excellence, or standing. See examples of best used in a sentence.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:21 UTC</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ae1a551d7e74</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Cars for Sale - Used Cars, New Cars, SUVs, and Trucks - Autotrader</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6ac74b890abf5212fa1e0d52a975cda1ce554a0ff12d8acc6b9695c75cfc941JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08f684d2-03ec-6783-3b76-93b502676668&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3RyYWRlci5jb20vP21zb2NraWQ9MDhmNjg0ZDIwM2VjNjc4MzNiNzY5M2I1MDI2NzY2Njg&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Explore new and used cars, trucks and SUVs with confidence. Autotrader is the one-stop shop for everything you need in your car buying experience including expert advice, instant cash offers, an …</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>8</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:27 UTC</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>604dfb76b1da</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Auto Parts at AutoZone - Batteries, Brakes, Accessories, and More</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=8474648f4bd73e5035a8f5f21596b210168b5ede985a767b13a2fed92f0b2930JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08f684d2-03ec-6783-3b76-93b502676668&amp;u=a1aHR0cHM6Ly93d3cuYXV0b3pvbmUuY29tLz9tc29ja2lkPTA4ZjY4NGQyMDNlYzY3ODMzYjc2OTNiNTAyNjc2NjY4&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Shop top-quality auto parts at AutoZone. Your go-to source for car and truck parts, DIY repair advice, and Free Next Day Delivery. Shop at over 6300 locations nationwide.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>7</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:27 UTC</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>a0dcadf7d152</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>O'Reilly Auto Parts | Auto Parts, Accessories, Repair Advice, &amp; More</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ccd47740571e244ee5a4578869716eb68c7567320c524767b2ed47cd1b5e035JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08f684d2-03ec-6783-3b76-93b502676668&amp;u=a1aHR0cHM6Ly93d3cub3JlaWxseWF1dG8uY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Find auto parts, tools, and more at O'Reilly Auto Parts. Shop online for FREE Next Day shipping or pick up your order at one of more than 6,000 stores.</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>7</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:27 UTC</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>6b1d62dd3e3c</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Used Cars for Sale in Camarillo, CA (with Photos) - CARFAX</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=c08284bf3ce755c226ad611e585278dba08edad4b753031809fe4d729068894aJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=08f684d2-03ec-6783-3b76-93b502676668&amp;u=a1aHR0cHM6Ly93d3cuY2FyZmF4LmNvbS9Vc2VkLUNhcnMtaW4tQ2FtYXJpbGxvLUNBX2MyNzA5Nj9tc29ja2lkPTA4ZjY4NGQyMDNlYzY3ODMzYjc2OTNiN</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Find the best used cars in Camarillo, CA. Every used car for sale comes with a free CARFAX Report. We have 2,362 used cars in Camarillo for sale that are reported accident free, 1,918 1-Owner cars, …</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:27 UTC</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>3df9144d3afd</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PAID Definition &amp; Meaning - Merriam-Webster</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a28f6507eaa639c0b69e117953cb9762666e49de2da65a1fc23cb0825f6a219JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=140c74de-e90e-650c-19ce-63b9e88c64a7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3BhaWQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>The meaning of PAID is past tense and past participle of pay. How to use paid in a sentence.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:32 UTC</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>6644ffe28370</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PAID Definition &amp; Meaning | Dictionary.com</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d5b267d19b73190f10136512aa0c793df6e5f83a720f7386c884216384010b0JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=140c74de-e90e-650c-19ce-63b9e88c64a7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3BhaWQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>PAID definition: a simple past tense and past participle of pay. See examples of paid used in a sentence.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:32 UTC</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>235e51b66fbb</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PAID | English meaning - Cambridge Dictionary</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8c19a92de905e176d84077d364b163002f207a3cb76ed3d99e56706c9d649b9JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=140c74de-e90e-650c-19ce-63b9e88c64a7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3BhaWQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>PAID definition: 1. past simple and past participle of pay 2. being given money for something: 3. used in…. Learn more.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:33 UTC</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>5e42387d37d0</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PAID definition in American English | Collins English Dictionary</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=79284c2454add53d9a1fc6808d745420ec2450841a32ae36b847e1acc7154011JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=140c74de-e90e-650c-19ce-63b9e88c64a7&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3VzL2RpY3Rpb25hcnkvZW5nbGlzaC9wYWlk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Paid means to do with the money a worker receives from his or her employer. You can say, for example, that someone is well paid when they receive a lot of money for the work that they do.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:33 UTC</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>f31bc5a1a02a</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Payed vs. Paid - Definition, Difference &amp; Examples - GRAMMARIST</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae4277a6d1c2e27f051550ff8aa777d8160f742bd88b46a97c7cf631493ab028JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=140c74de-e90e-650c-19ce-63b9e88c64a7&amp;u=a1aHR0cHM6Ly9ncmFtbWFyaXN0LmNvbS9zcGVsbGluZy9wYWlkLXBheWVkLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Both payed and paid are simple past forms of pay. But they have different definitions. Learn the difference in this article!</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:33 UTC</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ba195399fafc</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Paid - definition of paid by The Free Dictionary</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=555b2a6da10044896006b397c3efe1701b8256245a33f14f8605ac7b51422db0JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=140c74de-e90e-650c-19ce-63b9e88c64a7&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3BhaWQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>1. to discharge or settle (a debt, obligation, etc.), as by transferring money or goods, or by doing something. 2. to give over (money) in exchange for something. 3. to transfer money to (a person or …</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:33 UTC</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>6df955ab5a34</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Best Buy | Official Online Store | Shop Now &amp; Save</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=104af936d1e57b8f55df62d18b2f011e15c0ba67b77b34fcdbddf8ee9fc392ebJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fe781c3-5896-65a8-3524-96a459e2648e&amp;u=a1aHR0cHM6Ly93d3cuYmVzdGJ1eS5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Shop Best Buy for electronics, computers, appliances, cell phones, video games &amp; more new tech. Store pickup &amp; free 2-day shipping on thousands of items.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:39 UTC</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>4e4790470b47</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>BEST Definition &amp; Meaning - Merriam-Webster</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5f6972bc2817acc50d34273a18edc26d39e7c9578647179d97b4c9a6930492aJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fe781c3-5896-65a8-3524-96a459e2648e&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>May 21, 2026 · Cruise ships are perhaps best known for amenities like buffets and swimming pools, but their medical facilities also have the capability to treat a wide range of illnesses and injuries, from …</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:39 UTC</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>be44d064726b</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Best: Definition, Meaning, and Examples - usdictionary.com</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c5c98dda96c66192570823d6a942c3cd2944a4e43ea9ff702d54d27a09086c5JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fe781c3-5896-65a8-3524-96a459e2648e&amp;u=a1aHR0cHM6Ly91c2RpY3Rpb25hcnkuY29tL2RlZmluaXRpb25zL2Jlc3Qv&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Oct 14, 2024 · Explore the definition of the word "best," as well as its versatile usage, synonyms, examples, etymology, and more.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:39 UTC</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>0d7162be098e</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>BEST | English meaning - Cambridge Dictionary</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b83364c0304efdb7e62ac6c99b0f13fbed9c9e0b1ea37c04581183a35870a71JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fe781c3-5896-65a8-3524-96a459e2648e&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>BEST definition: 1. of the highest quality, or being the most suitable, pleasing, or effective type of thing or…. Learn more.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:39 UTC</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>f7c4bfa2ac04</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>best - WordReference.com Dictionary of English</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=8355922651e658100465e6c7774e92b04c83ed6dc2a2caf503556e176e190a84JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fe781c3-5896-65a8-3524-96a459e2648e&amp;u=a1aHR0cHM6Ly93d3cud29yZHJlZmVyZW5jZS5jb20vZGVmaW5pdGlvbi9iZXN0&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Affiliate</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Idioms (all) for the best, producing good as the final result: It turned out to be all for the best when I didn't get that job. Idioms as best one can, in the best way possible: As best I can tell, we're the first ones …</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:39 UTC</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>affiliate,referral</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>7ff2975a8d08</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>BEST Definition &amp; Meaning | Dictionary.com</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=8343a273726809bdba6765e2eb7f1b6cbfd947c34835e7ec853465d3178bbf7eJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fe781c3-5896-65a8-3524-96a459e2648e&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>BEST definition: of the highest quality, excellence, or standing. See examples of best used in a sentence.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:32:39 UTC</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>348a1463b343</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a79dbcc42456e59b845531ceeb14b74ba2a02433f4b3b722b3be6497c6d40bbJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa74169-b702-62d4-17a3-560eb6c76364&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0xZmE3NDE2OWI3MDI2MmQ0MTdhMzU2MGViNmM3NjM2NA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like Drift Boss, where one wrong turn sends you off the edge, or skill …</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:11 UTC</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>104b46f991da</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=cbd454307999077c56d7898be9a9c3c440081ba333319db4d51574418844f557JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa74169-b702-62d4-17a3-560eb6c76364&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:11 UTC</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>fce867e652ef</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=495d77ed285936c49234d8f7a2981488c26a8463955ee58bcf6240ca4755f8f5JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa74169-b702-62d4-17a3-560eb6c76364&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. Have fun!</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:11 UTC</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>52218e210dde</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc3cd8144f3958f59f5e61b590ec954726c51f58a843c69746f04cc502caf76aJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa74169-b702-62d4-17a3-560eb6c76364&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:12 UTC</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ed2e6d2ab457</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=5853b5d30e196cd5e5c0010fbc64b97e48b3a29be0845a9ef01400c9263ce31bJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa74169-b702-62d4-17a3-560eb6c76364&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, Crime and Comedy. Watch now.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:12 UTC</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>4b487cf19f9c</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=de9015b777cc92c1c127db537266498f2bfc3d12767233d51dbfe5c0198decbfJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa74169-b702-62d4-17a3-560eb6c76364&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and promo codes to save you over 50% on purchases.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:12 UTC</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>942b876c9c74</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=7458f81702d2433d690db2b511369a148c6c22a3b5732adae758a5b9c65b098bJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fa74169-b702-62d4-17a3-560eb6c76364&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) and Simon Kirke (drums, percussion).</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:12 UTC</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ff7c8f75a3dd</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Telegram Desktop - Free download and install on Windows | Microsoft …</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=80ea0f7e01e867d0f7c1d6c6b3bd7e72070e34563ff3e5f7d3833a3872472f76JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b37b0a3-7cf8-615f-1b3a-a7c47de460dd&amp;u=a1aHR0cHM6Ly9hcHBzLm1pY3Jvc29mdC5jb20vZGV0YWlsLzluenR3c3FudGQwcw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Apr 3, 2017 · We keep expanding the boundaries of what you can do with a messaging app. Don’t wait years for older messengers to catch up with …</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:24 UTC</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>9b97b9ad72ed</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Telegram - Download</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5e36c0f582bf7c3330766564c20c15a0bfbf40e1fc0f8e601e3c13c334cfe8fJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b37b0a3-7cf8-615f-1b3a-a7c47de460dd&amp;u=a1aHR0cHM6Ly90ZWxlZ3JhbS5lbi5zb2Z0b25pYy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Apr 14, 2026 · Telegram for Desktop offers a powerful, privacy-conscious messaging platform that caters to both casual and advanced users. With …</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>7</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:24 UTC</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>312f880ba0f0</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Download Telegram (free) for Windows, macOS, Android, APK ... - Gizmodo</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=380c3c797a9867ecbb206de86774511a2d7dd5d1ec8207e02c8d223ab2caf59cJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1b37b0a3-7cf8-615f-1b3a-a7c47de460dd&amp;u=a1aHR0cHM6Ly9naXptb2RvLmNvbS9kb3dubG9hZC90ZWxlZ3JhbQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>May 9, 2026 · Telegram is one of the most popular and secure communication apps today, with roughly a billion users.</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:24 UTC</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>4be270e8bdec</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a4158daa498e8fa50f3fad64e69823c4c33fbf297880b1ed902a76aa27938a5JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b44d771-6fdf-68c2-1da8-c0166e64698e&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0wYjQ0ZDc3MTZmZGY2OGMyMWRhOGMwMTY2ZTY0Njk4ZQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like Drift Boss, where one wrong turn sends you off the edge, or skill …</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:35 UTC</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1090707fedd6</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=e86709ecb7ab640cd486c8b6bb34773d16c8731c2ec7f92bf8c09ba075491e80JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b44d771-6fdf-68c2-1da8-c0166e64698e&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:35 UTC</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>6ce49ec92730</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=d269b6b3be89e7b6c02981436e29c23d41f50a0bc7a5db6d084132303c7c332dJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b44d771-6fdf-68c2-1da8-c0166e64698e&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. Have fun!</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:35 UTC</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>db1736ddf601</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=6daaf81c76450647024157a2d051bcdd7624dff5618a58e25299a1c8a355dee8JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b44d771-6fdf-68c2-1da8-c0166e64698e&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:35 UTC</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>c3fc447a4e53</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ebc8cff183d104365773d7ddf895dbad79333e1e5deb8690b7d88491722652bJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b44d771-6fdf-68c2-1da8-c0166e64698e&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, Crime and Comedy. Watch now.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:35 UTC</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ca5d19d05071</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4be83c221e478aa78b2fe71f50505cd8c545a008f169c7568d9b59822c95defJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b44d771-6fdf-68c2-1da8-c0166e64698e&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and promo codes to save you over 50% on purchases.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:35 UTC</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1bd0f318fa24</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=3834e9acdea2e378b46ef164a48c0764222db1ff1a263e00ede5a97546b8e044JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b44d771-6fdf-68c2-1da8-c0166e64698e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) and Simon Kirke (drums, percussion).</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:35 UTC</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2efac0cac822</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Best Buy | Official Online Store | Shop Now &amp; Save</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=949b3d8829db3311df150af4a9360638d26e7bf7617b8d06713e0caf0d09bee0JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e82efff-8108-63dc-18a3-f8988092620b&amp;u=a1aHR0cHM6Ly93d3cuYmVzdGJ1eS5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Shop Best Buy for electronics, computers, appliances, cell phones, video games &amp; more new tech. Store pickup &amp; free 2-day shipping on thousands of items.</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:54 UTC</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>7a1a0c01de93</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>BEST Definition &amp; Meaning - Merriam-Webster</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=48e94e3aa6410dfea9ec9252682afc27b2933379a7446f40250d77a68ad6a679JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e82efff-8108-63dc-18a3-f8988092620b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>May 21, 2026 · Cruise ships are perhaps best known for amenities like buffets and swimming pools, but their medical facilities also have the capability to treat a wide range of illnesses and injuries, from …</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:55 UTC</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2c9a690058a7</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Best: Definition, Meaning, and Examples - usdictionary.com</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd35b6307f38004bb28e6f86e11466223629246c38a36960ec02372cacb3ff9fJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e82efff-8108-63dc-18a3-f8988092620b&amp;u=a1aHR0cHM6Ly91c2RpY3Rpb25hcnkuY29tL2RlZmluaXRpb25zL2Jlc3Qv&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Oct 14, 2024 · Explore the definition of the word "best," as well as its versatile usage, synonyms, examples, etymology, and more.</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:55 UTC</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>59edca25782d</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>BEST | English meaning - Cambridge Dictionary</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=16e2dda800903ccefcba1c9f3aad51030b5c89a746830e34bbbcb7ab37503283JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e82efff-8108-63dc-18a3-f8988092620b&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>BEST definition: 1. of the highest quality, or being the most suitable, pleasing, or effective type of thing or…. Learn more.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:55 UTC</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>bb2fb555fb25</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>best - WordReference.com Dictionary of English</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bc015a73c0373911b6cb2e1904e3aa01198365754e00a109ec9b1b8254ba7d9JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e82efff-8108-63dc-18a3-f8988092620b&amp;u=a1aHR0cHM6Ly93d3cud29yZHJlZmVyZW5jZS5jb20vZGVmaW5pdGlvbi9iZXN0&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Affiliate</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Idioms (all) for the best, producing good as the final result: It turned out to be all for the best when I didn't get that job. Idioms as best one can, in the best way possible: As best I can tell, we're the first ones …</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:55 UTC</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>affiliate,referral</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2fe0cdc611ac</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>BEST Definition &amp; Meaning | Dictionary.com</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=e38fa693ab9b908367c8da746d30928042feef89793df780c3fcfe0ed02778dfJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2e82efff-8108-63dc-18a3-f8988092620b&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Jlc3Q&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>BEST definition: of the highest quality, excellence, or standing. See examples of best used in a sentence.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:33:55 UTC</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>9a72bb64f1df</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Speedtest by Ookla - The Global Broadband Speed Test</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6efd3e1b306ad3ae606eb5490b65d5c6a1be5bba19ee30929c0813ce43aa130JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e6275ff-b354-6614-3de4-6298b22a6708&amp;u=a1aHR0cHM6Ly93d3cuc3BlZWR0ZXN0Lm5ldC8&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Test your internet speed on any device with Speedtest by Ookla, available for free on desktop and mobile apps.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:00 UTC</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>46638637c665</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Speedtest di Ookla - Il test globale per la velocità della tua banda larga</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b1f7749600404b4854d08a1ef9b0ea0bc411c80ffc171558aecc7a02038bf32JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e6275ff-b354-6614-3de4-6298b22a6708&amp;u=a1aHR0cHM6Ly93d3cuc3BlZWR0ZXN0Lm5ldC9pdA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Test your internet speed with Speedtest by Ookla, a free and reliable tool for desktop and mobile devices.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:00 UTC</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>e0e059514ed7</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Speedtest od Ookla - globalny test prędkości łącza szerokopasmowego</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ae43282e4d07f992ce423487f2d6749631748d1f387acfbf8405aef3bec519dJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0e6275ff-b354-6614-3de4-6298b22a6708&amp;u=a1aHR0cHM6Ly93d3cuc3BlZWR0ZXN0Lm5ldC9wbA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Test your broadband speed with Speedtest by Ookla, available on all devices through free desktop and mobile apps.</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:00 UTC</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>a8e889cab377</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Welcome to Microsoft Rewards</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=9263a5d37b840727c953e9ffbe5e6f242e066c9fcc10031cf3276b0a125473d0JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly9yZXdhcmRzLmJpbmcuY29tL3dlbGNvbWU&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Earn free points with Microsoft Rewards that you can redeem for gift cards, use to enter sweepstakes, or donate to a nonprofit.</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>8</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:07 UTC</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>573fdc1f86cf</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>EARN Definition &amp; Meaning - Merriam-Webster</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5a1a486de9ba4bc34c4dbbee5086c83b8c6c2d38e013d519136befb86b7f742JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Vhcm4&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>May 21, 2026 · The meaning of EARN is to receive as return for effort and especially for work done or services rendered. How to use earn in a sentence.</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>1</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:07 UTC</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>42cba66ba954</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>EARN | English meaning - Cambridge Dictionary</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=49aa64feb0f753e5417a6b6a407715b093bc91499a0a632fd4ca433c10fe6ef5JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Vhcm4&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>EARN definition: 1. to receive money as payment for work that you do: 2. to get something that you deserve: 3. to…. Learn more.</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>1</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:07 UTC</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>86a3e7769436</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Earn - definition of earn by The Free Dictionary</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=4aa35d6a6990e0f4de4c328f9bb52bb8fd920d1e4fc0d04d1a48e99623fc2363JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Vhcm4&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>These verbs mean to gain as a result of one's behavior or effort: earns a large salary; deserves our thanks; a suggestion that merits consideration; an event that rates a mention in the news; a …</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>1</v>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:08 UTC</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>cb722b7a928a</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Making Money - NerdWallet</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=5febffb4dbbc6990320809eb2554ef7e1a59a5a06b8733c7424821a3bc8f405dJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly93d3cubmVyZHdhbGxldC5jb20vZmluYW5jZS9odWJzL21ha2luZy1tb25leT9tc29ja2lkPTAxNWEwNjRiYmEzYjYxNjAyM2JmMTEyY2JiZ</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Micro Tasks</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Find new ways to earn money through apps, side gigs and more online, offline and at home. Learn the key requirements for popular side hustles and how to start.</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:08 UTC</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>micro-task,freelance</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>47734cae88b0</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>EARN Definition &amp; Meaning | Dictionary.com</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=69c4c8e6a572a1e3f9ab2806de5e450a8352fd783121c51302a175d221d93e32JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Vhcm4&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>EARN definition: to gain or get in return for one's labor or service. See examples of earn used in a sentence.</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>1</v>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:08 UTC</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>c14e9e2d81e0</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>earn verb - Definition, pictures, pronunciation and usage notes ...</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=49cd24f5e1031a3f92d18e0f9ea09671b09c6bdf94da3c8ab54a5410c5744e6dJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly93d3cub3hmb3JkbGVhcm5lcnNkaWN0aW9uYXJpZXMuY29tL2RlZmluaXRpb24vZW5nbGlzaC9lYXJu&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Definition of earn verb in Oxford Advanced Learner's Dictionary. Meaning, pronunciation, picture, example sentences, grammar, usage notes, synonyms and more.</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>1</v>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:08 UTC</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>b4de6d5cf63c</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Earn Definition &amp; Meaning | Britannica Dictionary</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=aee3c5c8833cf8db0ccb91316ffb356a9a6657fda23fa06bc5a0a9476c039a19JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vZGljdGlvbmFyeS9lYXJu&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>He earned a promotion through hard work. The team has earned [= gained] a reputation for poor sportsmanship. She needs to earn [= gain, win] their trust/respect.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>1</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:08 UTC</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>120e571900b5</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Earn - Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=40bade2ca647b75554b0087927f395ee3cfbdf74452a109f3faf6282609cf894JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9lYXJu&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>When you earn something, you gain it as a result of your actions. You can earn your friend's gratitude by rescuing her pet kitten from a tree.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:08 UTC</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1a70611c3d25</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>EARN | definition in the Cambridge English Dictionary</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=02ea457e7fbb99830bb9fadfebe73694e6a7c365cba40ccb1b21a70fac9e1051JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=015a064b-ba3b-6160-23bf-112cbbf560d7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2Vhcm4&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>EARN meaning: 1. to receive money as payment for work that you do: 2. to get something that you deserve: 3. to…. Learn more.</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>1</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:08 UTC</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>36eb0aebdde6</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=dec28fd7498f3bf44edcb7fe956afa64c28873a49e64d2bad2b7135ff8940d12JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad91859-7c98-66ce-3e7b-0f3e7d1367b3&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0xYWQ5MTg1OTdjOTg2NmNlM2U3YjBmM2U3ZDEzNjdiMw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like Drift Boss, where one …</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:14 UTC</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>8b6cba8ccfe7</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=044e2641d7fcd06c877d23c5fbd3e6e5b80c2f0546354ea45f94c3c567a21097JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad91859-7c98-66ce-3e7b-0f3e7d1367b3&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:15 UTC</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>01f5f52bfba0</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=1913d959941e9391e2089a1449fa028f74d8b4891efb9effd7f3f655a9036612JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad91859-7c98-66ce-3e7b-0f3e7d1367b3&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. Have fun!</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:15 UTC</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>7e001d6902fb</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=48e096c1d8dd05bfe2e807e8db75d4cd228812c8ada61342612caa1e73ec6f89JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad91859-7c98-66ce-3e7b-0f3e7d1367b3&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>1</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:15 UTC</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>c84832bdca05</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=c59429576b8a8d725957246269b1a524ef38a5300512b0affc7b5ffe41337077JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad91859-7c98-66ce-3e7b-0f3e7d1367b3&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, Crime and Comedy. …</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:15 UTC</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>fcbafb39812f</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b2ec87a84e054589e51ffc9b48b58080fc41af4dca23a680043e5e7ba23f95fJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad91859-7c98-66ce-3e7b-0f3e7d1367b3&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and promo codes to save …</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:15 UTC</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>3209933b8f6f</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=43e936850cf5dd42d270fedcce5035ea827502a094ebc501bd48fd7905cda760JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad91859-7c98-66ce-3e7b-0f3e7d1367b3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) and Simon Kirke …</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>1</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:15 UTC</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>d3d18b35337c</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=f10be7377443aab571046400977e04191c66f1660f3b5e7e5dac1328c4b8ca66JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17278a23-b29d-66dc-0888-9d44b35a674d&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0xNzI3OGEyM2IyOWQ2NmRjMDg4ODlkNDRiMzVhNjc0ZA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like Drift Boss, where one wrong turn sends you off the edge, or skill …</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:38 UTC</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>96dcbf065364</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=491ee556eca8af4fe2ca3897b37097d81a9713bd80361a681992362bcf6f837bJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17278a23-b29d-66dc-0888-9d44b35a674d&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:38 UTC</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>e80084a92dd3</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=3dd30382a245a5280d6d2b6983860a24b923a8915d8e30f6e7f26bfb4facdd12JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17278a23-b29d-66dc-0888-9d44b35a674d&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. Have fun!</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:38 UTC</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>95c795455daf</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a0118e6c1c7edc9f80395b82599062b93aabdc298dd9dd8469b286f2e3babf5JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17278a23-b29d-66dc-0888-9d44b35a674d&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>1</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:38 UTC</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>d6e03f5324f1</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b095ef5ae07c035a6069ea6df7604bf52a86099f3d9ffadd18a4fda0149599dJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17278a23-b29d-66dc-0888-9d44b35a674d&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, Crime and Comedy. Watch now.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:38 UTC</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>e8acca58894b</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=240de52ca134d84074604713ba5051727ae535bc1b9adb1c511822e8f79acd0eJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17278a23-b29d-66dc-0888-9d44b35a674d&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and promo codes to save you over 50% on purchases.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:38 UTC</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>df13db6d68e1</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=fcad5258eb85a973ed9a31bdc7f8ee9d07d333871060dd0cdff59ee7eec042eeJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17278a23-b29d-66dc-0888-9d44b35a674d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) and Simon Kirke (drums, percussion).</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:39 UTC</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>a4ce8cafd102</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Cloud Computing Services - Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=26520eb78f50fde8fe2a369c9653dbedc445fb221d997909bc356ca45db71adbJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1df3b0ec-69b2-6267-15d9-a78b68ef63f8&amp;u=a1aHR0cHM6Ly9hd3MuYW1hem9uLmNvbS8&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Amazon Web Services offers reliable, scalable, and inexpensive cloud computing services. Free to join, pay only for what you use.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:45 UTC</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>17ba60b95d87</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>What is the cloud? | Learning Center - Cloudflare</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6e5bb69f9b6d028975ca6726fca5b803571fd41fec936fb8a772815c347b9dfJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1df3b0ec-69b2-6267-15d9-a78b68ef63f8&amp;u=a1aHR0cHM6Ly93d3cuY2xvdWRmbGFyZS5jb20vbGVhcm5pbmcvY2xvdWQvd2hhdC1pcy10aGUtY2xvdWQv&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Affiliate</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>The cloud refers to servers accessed over the Internet, and the software and databases that run on those servers.</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>6</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Medium: partially automatable</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:45 UTC</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>affiliate,referral</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>fc1b424dc02a</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Create and edit documents for free | Microsoft Word for the Web</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=db7ff261a788629f49e5e616ff755fbc7e7b1e3aeae381145a602416d9acca4aJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1df3b0ec-69b2-6267-15d9-a78b68ef63f8&amp;u=a1aHR0cHM6Ly93b3JkLmNsb3VkLm1pY3Jvc29mdC9lbi1nYi8&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Write, edit, and collaborate on documents online with Microsoft Word. Access seamlessly from any device for free.</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:45 UTC</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>5282bdbd44b2</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Web3 Architecture and Tech Stack - GeeksforGeeks</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e7f9a73d39e98988c3382ed79cc2dcff419afcd8c33cebd96943f1239cef129JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136c92c6-41fb-6631-2963-85a140fb6742&amp;u=a1aHR0cHM6Ly93d3cuZ2Vla3Nmb3JnZWVrcy5vcmcvY29tcHV0ZXItbmV0d29ya3Mvd2ViMy1hcmNoaXRlY3R1cmUtYW5kLXRlY2gtc3RhY2sv&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Affiliate</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Jul 23, 2025 · Web3 is the successor to Web2.0 (also referred to as Web2, aka the version of the World Wide Web currently used worldwide). It is built on …</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>6</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Medium: partially automatable</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:51 UTC</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>affiliate,referral</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ac4a6608fc7b</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Web3 - CoinDesk</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=84e77cf806bfdfb67b8b170064acc37bd0467fd7771db85246c0a21791a0b2d0JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136c92c6-41fb-6631-2963-85a140fb6742&amp;u=a1aHR0cHM6Ly93d3cuY29pbmRlc2suY29tL3dlYjM&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>May 5, 2026 · Leader in cryptocurrency, Bitcoin, Ethereum, XRP, blockchain, DeFi, digital finance and Web 3.0 news with analysis, video and live price …</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:51 UTC</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>972400040613</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Free Online Games at Poki - Play Now!</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=dbcd98c0d253a4e0ac8504cb99b5da5c7c2f8fd5e6ef5b1df4c64fbdd41fc08bJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0be534bd-d131-6228-1767-23dad00d63ef&amp;u=a1aHR0cHM6Ly9wb2tpLmNvbS8_bXNvY2tpZD0wYmU1MzRiZGQxMzE2MjI4MTc2NzIzZGFkMDBkNjNlZg&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Play 1500 free games instantly on Poki! All of the games are available to play on mobile, tablet and desktop. Try driving games like …</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:57 UTC</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>62f309b060ec</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Free Online Games on CrazyGames | Play Now!</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=27dc27fba390154c0536592af349c157fb1a716cefbb90c70b8cd9a6d1c502f1JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0be534bd-d131-6228-1767-23dad00d63ef&amp;u=a1aHR0cHM6Ly93d3cuY3JhenlnYW1lcy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Play free online games at CrazyGames, the best place to play high-quality browser games. We add new games every day. Have fun!</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:57 UTC</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>c700eff2ced2</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Play 100% Free Games | Instant &amp; Online | FreeGames.org</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=db71ea7bb098755e85920a12759962264cb8c4a55cc1131f0193c814acc62b74JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0be534bd-d131-6228-1767-23dad00d63ef&amp;u=a1aHR0cHM6Ly9mcmVlZ2FtZXMub3JnLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Free Games Our free online games can be played on PC, tablet or mobile with no downloads, purchases or disruptive video ads. …</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:58 UTC</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>622fd053f3b2</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Free Stuff near Beaverton, OR - craigslist</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=33ae457a7c1fc35f77399304ad40b40e93714a92e5ea7bc432ee8ad4b4e84143JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0be534bd-d131-6228-1767-23dad00d63ef&amp;u=a1aHR0cHM6Ly9wb3J0bGFuZC5jcmFpZ3NsaXN0Lm9yZy9zZWFyY2gvYmVhdmVydG9uLW9yL3ppcA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Free Couch and Ottoman! Seven 3-ring binders, assorted sizes, incl Tektronix if meaningful!</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:58 UTC</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>92c9f35cc6a8</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Watch Free Movies and TV Shows Online | Tubi</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=75d91dd6b3625208b8c195174f5e7bb1d64e27a1e5bf2009fa27cf77fbcfbd99JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0be534bd-d131-6228-1767-23dad00d63ef&amp;u=a1aHR0cHM6Ly90dWJpdHYuY29tLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Watch free movies and TV shows online in HD on any device. Tubi offers streaming movies in genres like Action, Horror, Sci-Fi, …</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:58 UTC</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>3daec0ec836c</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Free Stuff | Free Stuff Finder</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=05aa40375e7c8f76619d4834b38c7515cdf6a4d8a741b80cb72d3f7e55f0210dJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0be534bd-d131-6228-1767-23dad00d63ef&amp;u=a1aHR0cHM6Ly93d3cuZnJlZXN0dWZmZmluZGVyLmNvbS9mcmVlLXN0dWZmLw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>May 11, 2026 · Online free samples, freebies and how to get free stuff and products from companies. We also have coupons and …</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:58 UTC</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>b96f2314aae5</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Free (band) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=058f2e5c4598145413251ba99ab71f093b0455c8c2de6df4cfeef3819d5bcc74JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0be534bd-d131-6228-1767-23dad00d63ef&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRnJlZV8oYmFuZCk&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Free were an English rock band formed in London in 1968 by Paul Rodgers (vocals), Paul Kossoff (guitar), Andy Fraser (bass, piano) …</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>1</v>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:34:58 UTC</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1c9310866660</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>PASSIVE Definition &amp; Meaning - Merriam-Webster</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc4893bebb64d7891d5f9caacc9ad418fc3010b115cff04bd889a92962b25a5cJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3Bhc3NpdmU&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>4 days ago · passive implies immobility or lack of normally expected response to an external force or influence and often suggests deliberate submissiveness or self-control.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J273" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:09 UTC</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>8f3b3f7c4fa8</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>The Passive - Perfect English Grammar</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=096bac11241829d3efa828dba35ab8ca1a938dc9d7b7bdcfc3b205770ef018a1JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly93d3cucGVyZmVjdC1lbmdsaXNoLWdyYW1tYXIuY29tL3Bhc3NpdmUuaHRtbA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>We make the passive by putting the verb 'to be' into whatever tense we need and then adding the past participle. For regular verbs, we make the past participle by adding 'ed' to the infinitive.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J274" t="n">
+        <v>7</v>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:09 UTC</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>390114812fbf</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>PASSIVE Definition &amp; Meaning | Dictionary.com</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=4755af6992dee7e93a44e55252a77c179cecc09a8e8598e84c6f50469cc1d3baJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL3Bhc3NpdmU&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>PASSIVE definition: not reacting visibly to something that might be expected to produce manifestations of an emotion or feeling. See examples of passive used in a sentence.</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J275" t="n">
+        <v>1</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:10 UTC</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>e870f074937b</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>PASSIVE | English meaning - Cambridge Dictionary</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=af49659e35aa3b12790546b47768b672ade5049ba9b7c21d89381c938e545236JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL3Bhc3NpdmU&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>'Catrin told me' is an active sentence, and 'I was told by Catrin' is passive. In a passive sentence, the subject is the person or thing affected by the action of the verb.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J276" t="n">
+        <v>1</v>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:10 UTC</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>08d856eabe86</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Passive - definition of passive by The Free Dictionary</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ef7278efdda5f1a73a83ac12fa9d60b845acf3c2059a7f7095b741852d99c63JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL3Bhc3NpdmU&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Used to describe a form of verb in which the grammatical subject is the object of the action, for example, the sentence “The government took steps.” in the passive would be Steps were taken by the …</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>1</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:10 UTC</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>41bab873ab77</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Passives | LearnEnglish</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc296ee0a6fbfcfa2bf5fc8da59f75f0a0fc0c4414ad410b13a38f6dadb3acebJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly9sZWFybmVuZ2xpc2guYnJpdGlzaGNvdW5jaWwub3JnL2ZyZWUtcmVzb3VyY2VzL2dyYW1tYXIvYjEtYjIvcGFzc2l2ZXM&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Do you know how to use the passive voice to change the focus of a sentence? Test what you know with interactive exercises and read the explanation to help you.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J278" t="n">
+        <v>7</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:10 UTC</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>37d001c4e8a9</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>The Complete Guide to Passive Voice in English (With Clear …</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=579de3dbd5d181b58da62142477e0d44854ef092d7cb6d3122ede4d213d4c603JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly93d3cuaXdhbnRzcGVha2VuZ2xpc2guY29tL3Bvc3QvYS1jb21wbGV0ZS1ndWlkZS10by10aGUtcGFzc2l2ZS12b2ljZS1pbi1lbmdsaXNo&amp;</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Sep 19, 2025 · Don’t worry. In this complete guide, you’ll learn every passive tense in English, step by step — from basic forms to advanced structures — with clear examples and practice. Perfect for ESL …</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J279" t="n">
+        <v>7</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:10 UTC</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>b147078b79ae</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Passive - Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b68da91fb46d77036c0b1f9a5bd33e792af2f783105b2780fc7f00f23b325fcJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9wYXNzaXZl&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>When you're passive, you don't participate much and you're not very emotional. In chemistry, passive means to be "unreactive except under special or extreme conditions; inert."</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J280" t="n">
+        <v>1</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:10 UTC</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>3d9f87a088d8</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>PASSIVE definition and meaning | Collins English Dictionary</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6e0a4a3511d3e96165f2bbf44824b08ae9237b184efdef7bd4344b85496f26eJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL2RpY3Rpb25hcnkvZW5nbGlzaC9wYXNzaXZl&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>If you describe someone as passive, you mean that they do not take action but instead let things happen to them.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J281" t="n">
+        <v>1</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Educational content</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:10 UTC</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>f96cbae6b82e</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Active vs. Passive Voice: What's the Difference? | Grammarly</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e7871e11e25ed26b52a283796a80354bc9ec66e88db4fad617c5108548b9ae2JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ebf2205-c7fc-66b6-3c76-3562c6ea67d2&amp;u=a1aHR0cHM6Ly93d3cuZ3JhbW1hcmx5LmNvbS9ibG9nL3NlbnRlbmNlcy9hY3RpdmUtdnMtcGFzc2l2ZS12b2ljZS8_bXNvY2tpZD0wZWJmMjIwNWM3ZmM2N</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Nov 6, 2024 · Understand active voice vs. passive voice with these helpful guidelines and examples. Learn to use active voice and passive voice correctly in your writing.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J282" t="n">
+        <v>7</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:11 UTC</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>7682ed1ece12</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Telegram Desktop - Free download and install on Windows | Microsoft …</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=c451d4e75f95c41bc740989c98411a2f5d4bfd7036f609f25c0ca0afbddf312aJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148309-88cb-6eed-2855-946e89bf6f3e&amp;u=a1aHR0cHM6Ly9hcHBzLm1pY3Jvc29mdC5jb20vZGV0YWlsLzluenR3c3FudGQwcw&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Apr 3, 2017 · We keep expanding the boundaries of what you can do with a messaging app. Don’t wait years for older messengers to catch up with …</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:17 UTC</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>27661e131f1b</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Telegram - Download</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=0847995d542fe62b434d9f6c2dbdb09faf4c6ee50497f4fc575764dc00d274e6JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148309-88cb-6eed-2855-946e89bf6f3e&amp;u=a1aHR0cHM6Ly90ZWxlZ3JhbS5lbi5zb2Z0b25pYy5jb20v&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>DeFi / Staking</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Apr 14, 2026 · Telegram for Desktop offers a powerful, privacy-conscious messaging platform that caters to both casual and advanced users. With …</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J284" t="n">
+        <v>7</v>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>High automation: bot-friendly signals</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:17 UTC</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>defi,staking,yield</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>10ef6f4695e6</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Download Telegram (free) for Windows, macOS, Android, APK ... - Gizmodo</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=666d2bea109130d3c75f3348208a4792b19804ee4ed6975fa93f6a5d421a41b6JmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c148309-88cb-6eed-2855-946e89bf6f3e&amp;u=a1aHR0cHM6Ly9naXptb2RvLmNvbS9kb3dubG9hZC90ZWxlZ3JhbQ&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>May 9, 2026 · Telegram is one of the most popular and secure communication apps today, with roughly a billion users.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:17 UTC</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>5f3cfb8047c4</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Amazon.com: Faucet</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa74b51c991ecef9652b223f788e8f8d45958369e5e888d0e0f51d646fa605bdJmltdHM9MTc3OTg0MDAwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=301b6bf8-d591-61f8-0af9-7c9fd42c603e&amp;u=a1aHR0cHM6Ly93d3cuYW1hem9uLmNvbS9GYXVjZXQvcz9rPUZhdWNldA&amp;ntb=1</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Invest in a faucet built to last. Discover options with brass, stainless steel, or ceramic disc cartridges for reliable, drip-free operation.</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Low: no automation signals</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:35:22 UTC</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>money,earn</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
